--- a/config/anomaly-arbitration-generated/templates/AnomalyArbitrationReview.xlsx
+++ b/config/anomaly-arbitration-generated/templates/AnomalyArbitrationReview.xlsx
@@ -26,7 +26,7 @@
     <t>@table</t>
   </si>
   <si>
-    <t>AAMechanicRules</t>
+    <t>ArbMechanicRules</t>
   </si>
   <si>
     <t>@mode</t>
@@ -50,7 +50,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>2bebb13f740451a5</t>
+    <t>c2549c445ec65112</t>
   </si>
   <si>
     <t>#name</t>
@@ -113,16 +113,16 @@
     <t>string</t>
   </si>
   <si>
-    <t>enum&lt;AAOwnership&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AACoverageState&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AAEvidenceQuality&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AAMechanismQuality&gt;</t>
+    <t>enum&lt;ArbOwnership&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbCoverageState&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbEvidenceQuality&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbMechanismQuality&gt;</t>
   </si>
   <si>
     <t>list&lt;string&gt;</t>
@@ -167,10 +167,10 @@
     <t>#desc</t>
   </si>
   <si>
-    <t>AASources</t>
-  </si>
-  <si>
-    <t>a160294f91040008</t>
+    <t>ArbSources</t>
+  </si>
+  <si>
+    <t>a74a71234056172b</t>
   </si>
   <si>
     <t>source_id</t>
@@ -182,10 +182,10 @@
     <t>length=1..1000</t>
   </si>
   <si>
-    <t>AAReconciliation</t>
-  </si>
-  <si>
-    <t>9fb460ed8627b631</t>
+    <t>ArbReconciliation</t>
+  </si>
+  <si>
+    <t>574ae64068fc1d16</t>
   </si>
   <si>
     <t>source_path</t>
@@ -197,10 +197,10 @@
     <t>peer_goal_id</t>
   </si>
   <si>
-    <t>AACoverage</t>
-  </si>
-  <si>
-    <t>6fe609ef18a1e120</t>
+    <t>ArbCoverage</t>
+  </si>
+  <si>
+    <t>a73996e7684ea31f</t>
   </si>
   <si>
     <t>manifest_category</t>
@@ -209,10 +209,10 @@
     <t>manifest_record_id</t>
   </si>
   <si>
-    <t>AAResearchGaps</t>
-  </si>
-  <si>
-    <t>c2fbaf6dc51afcd1</t>
+    <t>ArbResearchGaps</t>
+  </si>
+  <si>
+    <t>1b1f6d4e57f37946</t>
   </si>
   <si>
     <t>blocking</t>
@@ -221,37 +221,37 @@
     <t>owner_batch</t>
   </si>
   <si>
-    <t>AAReviewFixtures</t>
-  </si>
-  <si>
-    <t>2672614ea4df2ce4</t>
+    <t>ArbReviewFixtures</t>
+  </si>
+  <si>
+    <t>db3b2f562b0c2426</t>
   </si>
   <si>
     <t>evidence_ref_ids</t>
   </si>
   <si>
-    <t>list&lt;ref&lt;AASources.id&gt;&gt;</t>
+    <t>list&lt;ref&lt;ArbSources.id&gt;&gt;</t>
   </si>
   <si>
     <t>parser=split;separator=|;length=1..1024</t>
   </si>
   <si>
-    <t>AAManifestReceipt</t>
-  </si>
-  <si>
-    <t>148c42a69c99fd4b</t>
+    <t>ArbManifestReceipt</t>
+  </si>
+  <si>
+    <t>3d82d8c88bec482f</t>
   </si>
   <si>
     <t>profile_id</t>
   </si>
   <si>
-    <t>ref&lt;AAProfiles.id&gt;</t>
-  </si>
-  <si>
-    <t>AAPackIndex</t>
-  </si>
-  <si>
-    <t>787d71319a798746</t>
+    <t>ref&lt;ArbProfiles.id&gt;</t>
+  </si>
+  <si>
+    <t>ArbPackIndex</t>
+  </si>
+  <si>
+    <t>d2fd8482cdb24f81</t>
   </si>
   <si>
     <t>file_order</t>
@@ -686,10 +686,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1015,16 +1015,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1043,10 +1043,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1388,16 +1388,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1416,10 +1416,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1777,16 +1777,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1805,10 +1805,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -2151,16 +2151,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2179,10 +2179,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -2522,16 +2522,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2553,16 +2553,16 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="23.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -2899,16 +2899,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2927,14 +2927,15 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
-    <col min="16" max="17" width="18.7109375" style="5" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -3253,16 +3254,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -3281,10 +3282,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -3626,16 +3627,16 @@
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
